--- a/stories/arbres/TREE-AUT-023.xlsx
+++ b/stories/arbres/TREE-AUT-023.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Maya est avec maman, à la maison. Maya a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya écoute maman. Maya entend les mots : reprendre ses affaires, avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Maya va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2537,6 +2590,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2701,6 +2759,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2926,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3093,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3260,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3427,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3594,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3761,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3861,6 +3954,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4025,6 +4123,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4290,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4457,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4624,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4791,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4958,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5125,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5185,6 +5318,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5487,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5654,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5821,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5988,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6155,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6322,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6351,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Maya va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6489,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6675,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6848,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6855,6 +7039,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7017,6 +7206,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7205,6 +7399,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7369,6 +7568,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7735,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7902,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8069,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8236,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8403,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8570,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8529,6 +8763,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8693,6 +8932,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9099,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9266,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9433,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9600,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9767,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9934,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9853,6 +10127,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10017,6 +10296,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10463,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10630,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10797,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10964,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11131,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10851,7 +11160,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Maya va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10989,6 +11298,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11169,6 +11484,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11523,6 +11848,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11685,6 +12015,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11873,6 +12208,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12037,6 +12377,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12544,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12711,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12878,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13045,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13212,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13379,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13197,6 +13572,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13361,6 +13741,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13908,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14075,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14242,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14409,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14576,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14743,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14521,6 +14936,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14685,6 +15105,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15272,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15439,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15606,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15773,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15940,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15586,6 +16036,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-023.xlsx
+++ b/stories/arbres/TREE-AUT-023.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Maya est avec maman, à la maison. Maya a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya écoute maman. Maya entend les mots : reprendre ses affaires, avant de partir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Maya a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2597,6 +2609,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2764,6 +2777,7 @@
           <t>narrateur|Maya rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2931,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3113,7 @@
           <t>narrateur|Maya rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3432,6 +3449,7 @@
           <t>narrateur|Maya rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3599,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3766,6 +3785,7 @@
           <t>narrateur|Maya a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4128,6 +4149,7 @@
           <t>narrateur|Maya rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4295,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4462,6 +4485,7 @@
           <t>narrateur|Maya rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4629,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4796,6 +4821,7 @@
           <t>narrateur|Maya rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4963,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +5157,7 @@
           <t>narrateur|Maya a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5325,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5492,6 +5521,7 @@
           <t>narrateur|Maya rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5659,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5826,6 +5857,7 @@
           <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5993,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,6 +6193,7 @@
           <t>narrateur|Maya rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6327,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6495,6 +6530,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6682,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6853,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7044,6 +7082,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7211,6 +7250,7 @@
           <t>narrateur|Maya a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7406,6 +7446,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7573,6 +7614,7 @@
           <t>narrateur|Maya rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7740,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7907,6 +7950,7 @@
           <t>narrateur|Maya rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8074,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8241,6 +8286,7 @@
           <t>narrateur|Maya rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8408,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8575,6 +8622,7 @@
           <t>narrateur|Maya a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8770,6 +8818,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8937,6 +8986,7 @@
           <t>narrateur|Maya rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9104,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9271,6 +9322,7 @@
           <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9438,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9605,6 +9658,7 @@
           <t>narrateur|Maya rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9772,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9939,6 +9994,7 @@
           <t>narrateur|Maya a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10134,6 +10190,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10301,6 +10358,7 @@
           <t>narrateur|Maya rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10468,6 +10526,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10635,6 +10694,7 @@
           <t>narrateur|Maya rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10802,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10969,6 +11030,7 @@
           <t>narrateur|Maya rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11136,6 +11198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11304,6 +11367,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11491,6 +11555,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11662,6 +11727,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11853,6 +11919,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12020,6 +12087,7 @@
           <t>narrateur|Maya a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12215,6 +12283,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12382,6 +12451,7 @@
           <t>narrateur|Maya rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12549,6 +12619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12716,6 +12787,7 @@
           <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12883,6 +12955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13050,6 +13123,7 @@
           <t>narrateur|Maya rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13217,6 +13291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13384,6 +13459,7 @@
           <t>narrateur|Maya a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13579,6 +13655,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13746,6 +13823,7 @@
           <t>narrateur|Maya rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13913,6 +13991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14080,6 +14159,7 @@
           <t>narrateur|Maya rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14247,6 +14327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14414,6 +14495,7 @@
           <t>narrateur|Maya rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14581,6 +14663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14748,6 +14831,7 @@
           <t>narrateur|Maya a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14943,6 +15027,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15110,6 +15195,7 @@
           <t>narrateur|Maya rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15277,6 +15363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15444,6 +15531,7 @@
           <t>narrateur|Maya rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15611,6 +15699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15778,6 +15867,7 @@
           <t>narrateur|Maya rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15945,6 +16035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15963,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16043,6 +16134,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16244,6 +16349,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-023.xlsx
+++ b/stories/arbres/TREE-AUT-023.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retrouver ses affaires avant de partir — à la maison</t>
+          <t>Le manteau sur la rampe</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina rentre du marché. Les fraises attendent dans le couloir. Elle joue au jardin de la maison. Avant de rentrer, elle cherche le seau et le manteau, et elle les prend.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Maya est avec maman, à la maison. Maya a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya écoute maman. Maya entend les mots : reprendre ses affaires, avant de partir.</t>
+          <t>L'escalier de bois fait cric, cric. Un panier de fraises attend dans le couloir. Ça sent le sucré, tout près. Le chat lèche sa patte, tout calme. Sur la rampe, un manteau rouge est posé. Le manteau est encore un peu chaud. Un seau jaune est sur une marche. Il y a du sable au fond. Papa pose le pain sur la table. Les fraises sont belles, Nina. On les goûtera tout à l'heure. En ce moment, Nina est dans le couloir. Elle a les mains un peu collantes. Je veux jouer dehors. D'accord. On va au jardin. Puis on va reprendre ses affaires. Avant de partir, on les cherche. Nina touche le manteau. Le tissu est doux sous les doigts. Le seau et le manteau, ma grande. On les cherche. On les prend. Je m'en souviens. Le jardin est juste derrière la porte. On entend un oiseau, tout petit. Tu as fini de te lécher les doigts ? Oui, maman. Alors on ouvre le jardin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,33 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Maya est avec maman, à la maison. Maya a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya écoute maman. Maya entend les mots : reprendre ses affaires, avant de partir.</t>
+          <t>narrateur|L'escalier de bois fait cric, cric.
+narrateur|Un panier de fraises attend dans le couloir.
+narrateur|Ça sent le sucré, tout près.
+narrateur|Le chat lèche sa patte, tout calme.
+narrateur|Sur la rampe, un manteau rouge est posé.
+narrateur|Le manteau est encore un peu chaud.
+narrateur|Un seau jaune est sur une marche.
+narrateur|Il y a du sable au fond.
+narrateur|Papa pose le pain sur la table.
+papa|Les fraises sont belles, Nina.
+maman|On les goûtera tout à l'heure.
+narrateur|En ce moment, Nina est dans le couloir.
+narrateur|Elle a les mains un peu collantes.
+enfant-f|Je veux jouer dehors.
+papa|D'accord. On va au jardin.
+maman|Puis on va reprendre ses affaires.
+maman|Avant de partir, on les cherche.
+narrateur|Nina touche le manteau.
+narrateur|Le tissu est doux sous les doigts.
+papa|Le seau et le manteau, ma grande.
+papa|On les cherche. On les prend.
+enfant-f|Je m'en souviens.
+narrateur|Le jardin est juste derrière la porte.
+narrateur|On entend un oiseau, tout petit.
+maman|Tu as fini de te lécher les doigts ?
+enfant-f|Oui, maman.
+papa|Alors on ouvre le jardin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1391,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Le jardin de la maison est calme. Tu veux le bac à sable, Nina ? Le toboggan, ou les balançoires ? Choisis. Ensuite on joue.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1559,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Le jardin de la maison est calme.
+papa|Tu veux le bac à sable, Nina ?
+maman|Le toboggan, ou les balançoires ?
+papa|Choisis. Ensuite on joue.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Nina pousse la porte du jardin. Le bois est un peu rêche. Le bac à sable est encore frais. Des grains collent à la planche. Une petite pelle dort dans le sable. Tu vas au bac, Nina ? Oui. Je veux le sable. On joue un peu. Puis on va reprendre ses affaires. Avant de partir, on les cherche. Nina pose les genoux dans le bac. Le sable est froid et doux. Le manteau rouge reste près du bac. Le seau jaune est à côté. Mon seau est là. Tu le verras, avant de partir. On le reprend. On le prend. Un oiseau picore près du banc. Bravo. Tu écoutes bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,8 +1730,25 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Nina pousse la porte du jardin.
+narrateur|Le bois est un peu rêche.
+narrateur|Le bac à sable est encore frais.
+narrateur|Des grains collent à la planche.
+narrateur|Une petite pelle dort dans le sable.
+maman|Tu vas au bac, Nina ?
+enfant-f|Oui. Je veux le sable.
+papa|On joue un peu.
+papa|Puis on va reprendre ses affaires.
+maman|Avant de partir, on les cherche.
+narrateur|Nina pose les genoux dans le bac.
+narrateur|Le sable est froid et doux.
+narrateur|Le manteau rouge reste près du bac.
+narrateur|Le seau jaune est à côté.
+enfant-f|Mon seau est là.
+maman|Tu le verras, avant de partir.
+papa|On le reprend. On le prend.
+narrateur|Un oiseau picore près du banc.
+papa|Bravo. Tu écoutes bien.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1718,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Bientôt on rentre. Nina a joué au bac à sable. Avant de partir, Nina fait quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1936,9 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|Bientôt on rentre.
+narrateur|Nina a joué au bac à sable.
+maman|Avant de partir, Nina fait quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. On va reprendre ses affaires. Avant de partir. Nina a joué au bac à sable. Elle cherche le seau. Elle cherche le manteau. Elle les prend. Bravo, Nina. Tu as fait du bon travail. On continue ? Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2110,17 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a joué au bac à sable.
+narrateur|Elle cherche le seau.
+narrateur|Elle cherche le manteau.
+narrateur|Elle les prend.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On continue ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2078,7 +2148,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Près du bac à sable, il y a des jouets. Le ballon, le seau, ou le doudou ? Choisis. Ensuite on reprend ses affaires.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2242,7 +2312,9 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Près du bac à sable, il y a des jouets.
+papa|Le ballon, le seau, ou le doudou ?
+maman|Choisis. Ensuite on reprend ses affaires.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2270,7 +2342,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>Près du bac, le ballon est rouge. Il a du sable dessus. Nina le pousse. Ça fait poum. Il rebondit, papa. Oui. Tout doux. Le ballon s'arrête près du seau. On va reprendre ses affaires. Avant de partir. Le ballon reste près du bac à sable. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,7 +2482,18 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Près du bac, le ballon est rouge.
+narrateur|Il a du sable dessus.
+narrateur|Nina le pousse. Ça fait poum.
+enfant-f|Il rebondit, papa.
+papa|Oui. Tout doux.
+narrateur|Le ballon s'arrête près du seau.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le ballon reste près du bac à sable.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2438,7 +2521,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le ballon, près du bac à sable. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2606,7 +2689,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le ballon, près du bac à sable.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2634,7 +2720,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le ballon avec elle. Elle a joué au bac à sable. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2774,7 +2860,27 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2802,7 +2908,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le ballon. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2942,7 +3048,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2970,7 +3085,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le ballon avec elle. Elle a joué au bac à sable. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3110,7 +3225,27 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3138,7 +3273,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le ballon. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3278,7 +3413,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3306,7 +3450,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le ballon avec elle. Elle a joué au bac à sable. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3446,7 +3590,27 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3474,7 +3638,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le ballon. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3614,7 +3778,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3642,7 +3815,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Près du bac, le seau jaune attend. Nina le remplit un peu. Le sable fait chh, dedans. Mon seau, maman. Oui. Tu le tiens. L'anse est un peu chaude. On va reprendre ses affaires. Avant de partir. Le seau reste près du bac à sable. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3782,7 +3955,18 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Près du bac, le seau jaune attend.
+narrateur|Nina le remplit un peu.
+narrateur|Le sable fait chh, dedans.
+enfant-f|Mon seau, maman.
+maman|Oui. Tu le tiens.
+narrateur|L'anse est un peu chaude.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le seau reste près du bac à sable.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3810,7 +3994,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le seau, près du bac à sable. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3978,7 +4162,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le seau, près du bac à sable.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4006,7 +4193,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le seau avec elle. Elle a joué au bac à sable. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,7 +4333,27 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4174,7 +4381,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le seau. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,7 +4521,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4342,7 +4558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le seau avec elle. Elle a joué au bac à sable. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,7 +4698,27 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4510,7 +4746,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le seau. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4650,7 +4886,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4678,7 +4923,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le seau avec elle. Elle a joué au bac à sable. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4818,7 +5063,27 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4846,7 +5111,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le seau. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4986,7 +5251,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5014,7 +5288,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>Près du bac, le doudou est gris. Il a une oreille dans le sable. Nina le secoue, tout doux. Il est sablé, papa. On le brosse un peu. Le doudou redevient doux. On va reprendre ses affaires. Avant de partir. Le doudou reste près du bac à sable. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5154,7 +5428,18 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Près du bac, le doudou est gris.
+narrateur|Il a une oreille dans le sable.
+narrateur|Nina le secoue, tout doux.
+enfant-f|Il est sablé, papa.
+papa|On le brosse un peu.
+narrateur|Le doudou redevient doux.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le doudou reste près du bac à sable.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5182,7 +5467,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le doudou, près du bac à sable. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,7 +5635,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le doudou, près du bac à sable.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5378,7 +5666,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le doudou avec elle. Elle a joué au bac à sable. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5518,7 +5806,27 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5546,7 +5854,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le doudou. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5686,7 +5994,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5714,7 +6031,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le doudou avec elle. Elle a joué au bac à sable. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5854,7 +6171,27 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5882,7 +6219,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le doudou. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6022,7 +6359,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6050,7 +6396,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le doudou avec elle. Elle a joué au bac à sable. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6190,7 +6536,27 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué au bac à sable.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6218,7 +6584,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle avait le doudou. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6358,7 +6724,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6386,7 +6761,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers le toboggan. Le métal est un peu tiède. Les marches sont étroites. Ça fait tic, sous les pieds. Tu montes une marche, Nina ? Oui, papa. Je glisse. On joue un peu. Puis on va reprendre ses affaires. Avant de partir, on les cherche. Nina glisse. Ça fait chhh. Le vent touche ses joues. Le manteau attend au pied. Le seau est près de la première marche. Je redescends. On reprend le seau et le manteau. On les prend, avant de partir. Une feuille colle au métal. Bravo. Tu as glissé doucement.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6526,8 +6901,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Maya va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Nina va vers le toboggan.
+narrateur|Le métal est un peu tiède.
+narrateur|Les marches sont étroites.
+narrateur|Ça fait tic, sous les pieds.
+papa|Tu montes une marche, Nina ?
+enfant-f|Oui, papa. Je glisse.
+maman|On joue un peu.
+maman|Puis on va reprendre ses affaires.
+papa|Avant de partir, on les cherche.
+narrateur|Nina glisse. Ça fait chhh.
+narrateur|Le vent touche ses joues.
+narrateur|Le manteau attend au pied.
+narrateur|Le seau est près de la première marche.
+enfant-f|Je redescends.
+papa|On reprend le seau et le manteau.
+maman|On les prend, avant de partir.
+narrateur|Une feuille colle au métal.
+maman|Bravo. Tu as glissé doucement.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6555,7 +6946,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Bientôt on rentre. Nina a joué au toboggan. Avant de partir, Nina fait quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6715,7 +7106,9 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|Bientôt on rentre.
+narrateur|Nina a joué au toboggan.
+maman|Avant de partir, Nina fait quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6743,7 +7136,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. On va reprendre ses affaires. Avant de partir. Nina a joué au toboggan. Elle cherche le seau. Elle cherche le manteau. Elle les prend. Bravo, Nina. Tu as fait du bon travail. On continue ? Oui, maman.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6887,7 +7280,17 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a joué au toboggan.
+narrateur|Elle cherche le seau.
+narrateur|Elle cherche le manteau.
+narrateur|Elle les prend.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On continue ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6915,7 +7318,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Près du toboggan, il y a des jouets. Le ballon, le seau, ou le doudou ? Choisis. Ensuite on reprend ses affaires.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7079,7 +7482,9 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Près du toboggan, il y a des jouets.
+papa|Le ballon, le seau, ou le doudou ?
+maman|Choisis. Ensuite on reprend ses affaires.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7107,7 +7512,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>Au pied du toboggan, le ballon attend. Il est un peu chaud du soleil. Nina le prend à deux mains. Il est gros, maman. Oui. Tu le tiens bien. Le ballon sent le caoutchouc. On va reprendre ses affaires. Avant de partir. Le ballon reste près du toboggan. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7247,7 +7652,18 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Au pied du toboggan, le ballon attend.
+narrateur|Il est un peu chaud du soleil.
+narrateur|Nina le prend à deux mains.
+enfant-f|Il est gros, maman.
+maman|Oui. Tu le tiens bien.
+narrateur|Le ballon sent le caoutchouc.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le ballon reste près du toboggan.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7275,7 +7691,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le ballon, près du toboggan. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7443,7 +7859,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le ballon, près du toboggan.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7471,7 +7890,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le ballon avec elle. Elle a joué au toboggan. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7611,7 +8030,27 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7639,7 +8078,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le ballon. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7779,7 +8218,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7807,7 +8255,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le ballon avec elle. Elle a joué au toboggan. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7947,7 +8395,27 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7975,7 +8443,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le ballon. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8115,7 +8583,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8143,7 +8620,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le ballon avec elle. Elle a joué au toboggan. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8283,7 +8760,27 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8311,7 +8808,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le ballon. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8451,7 +8948,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8479,7 +8985,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sur la première marche, le seau est là. Nina le descend, tout lentement. Ça fait toc, contre le bois. Je l'ai, papa. Tu le prends. Bravo. Il reste un grain de sable dedans. On va reprendre ses affaires. Avant de partir. Le seau reste près du toboggan. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8619,7 +9125,18 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Sur la première marche, le seau est là.
+narrateur|Nina le descend, tout lentement.
+narrateur|Ça fait toc, contre le bois.
+enfant-f|Je l'ai, papa.
+papa|Tu le prends. Bravo.
+narrateur|Il reste un grain de sable dedans.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le seau reste près du toboggan.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8647,7 +9164,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le seau, près du toboggan. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8815,7 +9332,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le seau, près du toboggan.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8843,7 +9363,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le seau avec elle. Elle a joué au toboggan. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8983,7 +9503,27 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9011,7 +9551,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le seau. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9151,7 +9691,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9179,7 +9728,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le seau avec elle. Elle a joué au toboggan. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9319,7 +9868,27 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9347,7 +9916,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le seau. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9487,7 +10056,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9515,7 +10093,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le seau avec elle. Elle a joué au toboggan. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9655,7 +10233,27 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9683,7 +10281,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le seau. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9823,7 +10421,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9851,7 +10458,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>Sur le siège du toboggan, le doudou dort. Nina le prend contre sa joue. Le tissu est un peu tiède. Il a glissé avec moi. Oui. Tu le tiens. Le doudou sent le vent. On va reprendre ses affaires. Avant de partir. Le doudou reste près du toboggan. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9991,7 +10598,18 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Sur le siège du toboggan, le doudou dort.
+narrateur|Nina le prend contre sa joue.
+narrateur|Le tissu est un peu tiède.
+enfant-f|Il a glissé avec moi.
+maman|Oui. Tu le tiens.
+narrateur|Le doudou sent le vent.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le doudou reste près du toboggan.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10019,7 +10637,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le doudou, près du toboggan. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10187,7 +10805,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le doudou, près du toboggan.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10215,7 +10836,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le doudou avec elle. Elle a joué au toboggan. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10355,7 +10976,27 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10383,7 +11024,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le doudou. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10523,7 +11164,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10551,7 +11201,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le doudou avec elle. Elle a joué au toboggan. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10691,7 +11341,27 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10719,7 +11389,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le doudou. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10859,7 +11529,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10887,7 +11566,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le doudou avec elle. Elle a joué au toboggan. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11027,7 +11706,27 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué au toboggan.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11055,7 +11754,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle avait le doudou. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11195,7 +11894,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11223,7 +11931,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers les balançoires. La chaîne fait un petit tic. Le siège en bois est lisse. L'herbe est un peu mouillée. Tu te mets dessus, Nina ? Oui. Tout doucement. On joue un peu. Puis on va reprendre ses affaires. Avant de partir, on les cherche. Nina pose les mains sur la chaîne. Le métal est frais. Le manteau rouge est sur l'herbe. Le seau jaune est sous le siège. Je me balance. On reprend le seau et le manteau. On les prend, avant de partir. Un papillon passe, tout bas. Bravo. Tu es bien assise.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11363,8 +12071,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Maya va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Maya se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Nina va vers les balançoires.
+narrateur|La chaîne fait un petit tic.
+narrateur|Le siège en bois est lisse.
+narrateur|L'herbe est un peu mouillée.
+maman|Tu te mets dessus, Nina ?
+enfant-f|Oui. Tout doucement.
+papa|On joue un peu.
+papa|Puis on va reprendre ses affaires.
+maman|Avant de partir, on les cherche.
+narrateur|Nina pose les mains sur la chaîne.
+narrateur|Le métal est frais.
+narrateur|Le manteau rouge est sur l'herbe.
+narrateur|Le seau jaune est sous le siège.
+enfant-f|Je me balance.
+maman|On reprend le seau et le manteau.
+papa|On les prend, avant de partir.
+narrateur|Un papillon passe, tout bas.
+papa|Bravo. Tu es bien assise.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11392,7 +12116,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Bientôt on rentre. Nina a joué aux balançoires. Avant de partir, Nina fait quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11552,7 +12276,9 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|Bientôt on rentre.
+narrateur|Nina a joué aux balançoires.
+maman|Avant de partir, Nina fait quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11580,7 +12306,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. On va reprendre ses affaires. Avant de partir. Nina a joué aux balançoires. Elle cherche le seau. Elle cherche le manteau. Elle les prend. Bravo, Nina. Tu as fait du bon travail. On continue ? Oui, maman.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11724,7 +12450,17 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Maya respire. Maya retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a joué aux balançoires.
+narrateur|Elle cherche le seau.
+narrateur|Elle cherche le manteau.
+narrateur|Elle les prend.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On continue ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11752,7 +12488,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Près des balançoires, il y a des jouets. Le ballon, le seau, ou le doudou ? Choisis. Ensuite on reprend ses affaires.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11916,7 +12652,9 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Près des balançoires, il y a des jouets.
+papa|Le ballon, le seau, ou le doudou ?
+maman|Choisis. Ensuite on reprend ses affaires.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11944,7 +12682,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>Près du poteau, le ballon est rouge. Il roule dans l'herbe mouillée. Nina l'attrape. Il est froid. Il est mouillé, papa. On l'essuie un peu. L'herbe laisse une trace verte. On va reprendre ses affaires. Avant de partir. Le ballon reste près des balançoires. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12084,7 +12822,18 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Près du poteau, le ballon est rouge.
+narrateur|Il roule dans l'herbe mouillée.
+narrateur|Nina l'attrape. Il est froid.
+enfant-f|Il est mouillé, papa.
+papa|On l'essuie un peu.
+narrateur|L'herbe laisse une trace verte.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le ballon reste près des balançoires.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12112,7 +12861,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le ballon, près des balançoires. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12280,7 +13029,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le ballon, près des balançoires.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12308,7 +13060,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le ballon avec elle. Elle a joué aux balançoires. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12448,7 +13200,27 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12476,7 +13248,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le ballon. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12616,7 +13388,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12644,7 +13425,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le ballon avec elle. Elle a joué aux balançoires. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12784,7 +13565,27 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12812,7 +13613,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le ballon. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12952,7 +13753,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12980,7 +13790,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le ballon avec elle. Elle a joué aux balançoires. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13120,7 +13930,27 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le ballon avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13148,7 +13978,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le ballon. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13288,7 +14118,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le ballon.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13316,7 +14155,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sous le siège, le seau jaune attend. Nina se baisse. Elle le prend. L'herbe chatouille ses genoux. Je l'ai, maman. Tu le prends. Bravo. Le seau a une feuille dedans. On va reprendre ses affaires. Avant de partir. Le seau reste près des balançoires. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13456,7 +14295,18 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Sous le siège, le seau jaune attend.
+narrateur|Nina se baisse. Elle le prend.
+narrateur|L'herbe chatouille ses genoux.
+enfant-f|Je l'ai, maman.
+maman|Tu le prends. Bravo.
+narrateur|Le seau a une feuille dedans.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le seau reste près des balançoires.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13484,7 +14334,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le seau, près des balançoires. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13652,7 +14502,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le seau, près des balançoires.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13680,7 +14533,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le seau avec elle. Elle a joué aux balançoires. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13820,7 +14673,27 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13848,7 +14721,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le seau. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13988,7 +14861,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14016,7 +14898,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le seau avec elle. Elle a joué aux balançoires. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14156,7 +15038,27 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14184,7 +15086,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le seau. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14324,7 +15226,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14352,7 +15263,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le seau avec elle. Elle a joué aux balançoires. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14492,7 +15403,27 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le seau avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14520,7 +15451,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le seau. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14660,7 +15591,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le seau.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14688,7 +15628,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>Sur le siège, le doudou est gris. Il va et vient, tout doux. Nina le serre contre elle. Il se balance, papa. Oui. Tu le tiens bien. Le doudou a une odeur de savon. On va reprendre ses affaires. Avant de partir. Le doudou reste près des balançoires. Le seau et le manteau aussi. On les cherche. Oui. On les prend.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14828,7 +15768,18 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Maya répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Sur le siège, le doudou est gris.
+narrateur|Il va et vient, tout doux.
+narrateur|Nina le serre contre elle.
+enfant-f|Il se balance, papa.
+papa|Oui. Tu le tiens bien.
+narrateur|Le doudou a une odeur de savon.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Le doudou reste près des balançoires.
+papa|Le seau et le manteau aussi.
+enfant-f|On les cherche.
+maman|Oui. On les prend.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14856,7 +15807,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Nina a le doudou, près des balançoires. On va vers le banc, le portail, ou le paillasson ? Ensuite on va reprendre ses affaires. Avant de partir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15024,7 +15975,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Nina a le doudou, près des balançoires.
+maman|On va vers le banc, le portail, ou le paillasson ?
+papa|Ensuite on va reprendre ses affaires.
+papa|Avant de partir.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15052,7 +16006,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le banc. Le bois des lattes est chaud. Une fourmi marche sur le bord. Le banc est chaud, maman. Oui. On s'assoit un peu. Elle a encore le doudou avec elle. Elle a joué aux balançoires. Sous le banc, le manteau rouge attend. Nina le tire, tout doucement. J'ai le manteau. Tu le prends. Bravo. Le seau est près de ses pieds. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15192,7 +16146,27 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le banc.
+narrateur|Le bois des lattes est chaud.
+narrateur|Une fourmi marche sur le bord.
+enfant-f|Le banc est chaud, maman.
+maman|Oui. On s'assoit un peu.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Sous le banc, le manteau rouge attend.
+narrateur|Nina le tire, tout doucement.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est près de ses pieds.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15220,7 +16194,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le doudou. Elle est passée par le banc. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15360,7 +16334,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le banc.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15388,7 +16371,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le portail. Le loquet est un peu froid. Le portail fait criiic. J'entends le criiic, papa. Oui. On pousse tout doux. Elle a encore le doudou avec elle. Elle a joué aux balançoires. Près du loquet, le seau jaune attend. Nina le saisit par l'anse. J'ai le seau. Tu le prends. Bravo. Le manteau est accroché au bois. Nina le décroche. Elle le prend. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15528,7 +16511,27 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le portail.
+narrateur|Le loquet est un peu froid.
+narrateur|Le portail fait criiic.
+enfant-f|J'entends le criiic, papa.
+papa|Oui. On pousse tout doux.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Près du loquet, le seau jaune attend.
+narrateur|Nina le saisit par l'anse.
+enfant-f|J'ai le seau.
+maman|Tu le prends. Bravo.
+narrateur|Le manteau est accroché au bois.
+narrateur|Nina le décroche. Elle le prend.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15556,7 +16559,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le doudou. Elle est passée par le portail. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15696,7 +16699,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le portail.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15724,7 +16736,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>Nina va vers le paillasson. Il est rêche, couleur paille. Les chaussures attendent dessus. Ça pique un peu, maman. Oui. C'est le paillasson. Elle a encore le doudou avec elle. Elle a joué aux balançoires. Sur le paillasson, le manteau est plié. Nina le soulève. Il est doux. J'ai le manteau. Tu le prends. Bravo. Le seau est contre le seuil. Nina le prend aussi. On va reprendre ses affaires. Avant de partir. Nina a le seau. Nina a le manteau. J'ai tout. Bravo, Nina. Tu as fait du bon travail. Les fraises nous attendent. On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15864,7 +16876,27 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Maya a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Maya a entendu : reprendre ses affaires, avant de partir. Maya dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina va vers le paillasson.
+narrateur|Il est rêche, couleur paille.
+narrateur|Les chaussures attendent dessus.
+enfant-f|Ça pique un peu, maman.
+maman|Oui. C'est le paillasson.
+narrateur|Elle a encore le doudou avec elle.
+narrateur|Elle a joué aux balançoires.
+narrateur|Sur le paillasson, le manteau est plié.
+narrateur|Nina le soulève. Il est doux.
+enfant-f|J'ai le manteau.
+papa|Tu le prends. Bravo.
+narrateur|Le seau est contre le seuil.
+narrateur|Nina le prend aussi.
+papa|On va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Nina a le seau.
+narrateur|Nina a le manteau.
+enfant-f|J'ai tout.
+papa|Bravo, Nina. Tu as fait du bon travail.
+maman|Les fraises nous attendent.
+narrateur|On rentre. Le chat lève la tête.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15892,7 +16924,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle avait le doudou. Elle est passée par le paillasson. J'ai le seau. J'ai le manteau. Nina va reprendre ses affaires. Avant de partir. Bravo, Nina. Tu as fait du bon travail. Le panier de fraises sent encore. Le chat se recouche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16032,7 +17064,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle avait le doudou.
+narrateur|Elle est passée par le paillasson.
+enfant-f|J'ai le seau. J'ai le manteau.
+papa|Nina va reprendre ses affaires.
+maman|Avant de partir.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le panier de fraises sent encore.
+narrateur|Le chat se recouche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16054,7 +17095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16148,6 +17189,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-023.xlsx
+++ b/stories/arbres/TREE-AUT-023.xlsx
@@ -2748,17 +2748,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le grain a failli tout cacher. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Un grain cachait le croissant, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le grain a failli tout cacher. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Un grain cachait le croissant, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le grain a failli tout cacher. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Un grain cachait le croissant, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Un grain de sable reste au croissant.
-narrateur|Le grain a failli tout cacher.
+narrateur|Un grain cachait le croissant, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -3139,17 +3139,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le loquet a failli tout garder. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le loquet serrait trop, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le loquet a failli tout garder. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le loquet serrait trop, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le loquet a failli tout garder. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. Le loquet serrait trop, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Un grain de sable reste au croissant.
-narrateur|Le loquet a failli tout garder.
+narrateur|Le loquet serrait trop, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -3339,17 +3339,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Le couloir sent les fraises, plus fort. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le loquet garde un fil rouge.</t>
+          <t>Le couloir sent les fraises, plus fort. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le loquet garde un fil rouge, minuscule.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le couloir sent les fraises, plus fort. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le loquet garde un fil rouge.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le couloir sent les fraises, plus fort. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le loquet garde un fil rouge, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le couloir sent les fraises, plus fort. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le loquet garde un fil rouge.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le couloir sent les fraises, plus fort. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le loquet garde un fil rouge, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le loquet garde un fil rouge.</t>
+narrateur|Le loquet garde un fil rouge, minuscule.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -3530,17 +3530,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. La paille a failli tout plier. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. La paille recouvrait le col, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. La paille a failli tout plier. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. La paille recouvrait le col, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. La paille a failli tout plier. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. Un grain de sable reste au croissant. La paille recouvrait le col, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Un grain de sable reste au croissant.
-narrateur|La paille a failli tout plier.
+narrateur|La paille recouvrait le col, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -3730,17 +3730,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Le chat se recouche, sous la rampe. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le paillasson tient un grain, minuscule.</t>
+          <t>Le chat se recouche, sous la rampe. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un grain reste coincé dans la paille.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chat se recouche, sous la rampe. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le paillasson tient un grain, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chat se recouche, sous la rampe. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un grain reste coincé dans la paille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chat se recouche, sous la rampe. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le paillasson tient un grain, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chat se recouche, sous la rampe. Chouchou a joué au bac. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un grain reste coincé dans la paille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le paillasson tient un grain, minuscule.</t>
+narrateur|Un grain reste coincé dans la paille.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4312,17 +4312,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le sable a failli tout boire. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le sable buvait la manche, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le sable a failli tout boire. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le sable buvait la manche, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le sable a failli tout boire. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le sable buvait la manche, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4479,7 +4479,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'anse du seau a laissé du sable.
-narrateur|Le sable a failli tout boire.
+narrateur|Le sable buvait la manche, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -4512,17 +4512,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Un grain roule sur une marche. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'anse du seau sèche sous la rampe.</t>
+          <t>Un grain roule sur une marche. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'anse du seau sèche, sous la rampe.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un grain roule sur une marche. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'anse du seau sèche sous la rampe.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un grain roule sur une marche. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'anse du seau sèche, sous la rampe.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un grain roule sur une marche. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'anse du seau sèche sous la rampe.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un grain roule sur une marche. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'anse du seau sèche, sous la rampe.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|L'anse du seau sèche sous la rampe.</t>
+narrateur|L'anse du seau sèche, sous la rampe.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. L'anse a failli tout tirer. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. L'anse tirait trop, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. L'anse a failli tout tirer. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. L'anse tirait trop, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. L'anse a failli tout tirer. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. L'anse tirait trop, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4870,7 +4870,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'anse du seau a laissé du sable.
-narrateur|L'anse a failli tout tirer.
+narrateur|L'anse tirait trop, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -4903,17 +4903,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Le seau pose son ombre au bois. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise roule près du pain.</t>
+          <t>Le seau pose son ombre au bois. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise roule près du pain tiède.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau pose son ombre au bois. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise roule près du pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau pose son ombre au bois. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise roule près du pain tiède.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau pose son ombre au bois. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise roule près du pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau pose son ombre au bois. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise roule près du pain tiède.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -5062,7 +5062,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Une fraise roule près du pain.</t>
+narrateur|Une fraise roule près du pain tiède.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -5094,17 +5094,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le seuil a failli tout garder. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le seuil gardait le pli, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le seuil a failli tout garder. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le seuil gardait le pli, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le seuil a failli tout garder. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'anse du seau a laissé du sable. Le seuil gardait le pli, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5261,7 +5261,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'anse du seau a laissé du sable.
-narrateur|Le seuil a failli tout garder.
+narrateur|Le seuil gardait le pli, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -5294,17 +5294,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Le panier de fraises attend, ouvert. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau pose son ombre au seuil.</t>
+          <t>Le panier de fraises attend, ouvert. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'ombre du seau s'endort au seuil.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le panier de fraises attend, ouvert. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau pose son ombre au seuil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le panier de fraises attend, ouvert. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'ombre du seau s'endort au seuil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le panier de fraises attend, ouvert. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau pose son ombre au seuil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le panier de fraises attend, ouvert. Chouchou a joué au bac. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'ombre du seau s'endort au seuil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5453,7 +5453,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le seau pose son ombre au seuil.</t>
+narrateur|L'ombre du seau s'endort au seuil.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le doudou a failli tout cacher. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le doudou cachait le rouge, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le doudou a failli tout cacher. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le doudou cachait le rouge, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le doudou a failli tout cacher. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le doudou cachait le rouge, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -6043,7 +6043,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'oreille du doudou a du sable.
-narrateur|Le doudou a failli tout cacher.
+narrateur|Le doudou cachait le rouge, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -6076,17 +6076,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'oreille du doudou dépasse du couloir. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'oreille du doudou veille, au bois.</t>
+          <t>L'oreille du doudou dépasse du couloir. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Du sable reste dans l'oreille du doudou.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille du doudou dépasse du couloir. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'oreille du doudou veille, au bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille du doudou dépasse du couloir. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Du sable reste dans l'oreille du doudou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille du doudou dépasse du couloir. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'oreille du doudou veille, au bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille du doudou dépasse du couloir. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Du sable reste dans l'oreille du doudou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6235,7 +6235,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|L'oreille du doudou veille, au bois.</t>
+narrateur|Du sable reste dans l'oreille du doudou.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -6267,17 +6267,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le fer a failli tout mordre. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le fer mordait la manche, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le fer a failli tout mordre. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le fer mordait la manche, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le fer a failli tout mordre. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le fer mordait la manche, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6434,7 +6434,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'oreille du doudou a du sable.
-narrateur|Le fer a failli tout mordre.
+narrateur|Le fer mordait la manche, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -6467,17 +6467,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Un fil du doudou pend près des clés. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un fil gris pend près des clés.</t>
+          <t>Un fil du doudou pend près des clés. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près des clés, un fil gris pend.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un fil du doudou pend près des clés. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un fil gris pend près des clés.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un fil du doudou pend près des clés. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près des clés, un fil gris pend.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un fil du doudou pend près des clés. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un fil gris pend près des clés.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un fil du doudou pend près des clés. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près des clés, un fil gris pend.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Un fil gris pend près des clés.</t>
+narrateur|Près des clés, un fil gris pend.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -6658,17 +6658,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le pli a failli tout perdre. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le pli se refermait, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le pli a failli tout perdre. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le pli se refermait, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le pli a failli tout perdre. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le bac, croissant en main. On va au crochet, maintenant. L'oreille du doudou a du sable. Le pli se refermait, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6825,7 +6825,7 @@
 narrateur|On quitte le bac, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'oreille du doudou a du sable.
-narrateur|Le pli a failli tout perdre.
+narrateur|Le pli se refermait, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -6858,17 +6858,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le doudou sent le sable, au bois. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou garde le sable, au col.</t>
+          <t>Le doudou sent le sable, au bois. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au col, un grain de sable brille.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou sent le sable, au bois. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou garde le sable, au col.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou sent le sable, au bois. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au col, un grain de sable brille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou sent le sable, au bois. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou garde le sable, au col.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou sent le sable, au bois. Chouchou a joué au bac. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au col, un grain de sable brille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -7017,7 +7017,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le doudou garde le sable, au col.</t>
+narrateur|Au col, un grain de sable brille.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -8199,17 +8199,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. La feuille a failli tout couvrir. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Une feuille couvrait le col, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. La feuille a failli tout couvrir. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Une feuille couvrait le col, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. La feuille a failli tout couvrir. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Une feuille couvrait le col, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8366,7 +8366,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une feuille du toboggan reste au tissu.
-narrateur|La feuille a failli tout couvrir.
+narrateur|Une feuille couvrait le col, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -8399,17 +8399,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Une feuille sèche sur le banc, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une feuille sèche, loin du croissant.</t>
+          <t>Une feuille sèche sur le banc, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une feuille sèche, collée au croissant.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une feuille sèche sur le banc, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une feuille sèche, loin du croissant.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une feuille sèche sur le banc, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une feuille sèche, collée au croissant.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une feuille sèche sur le banc, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une feuille sèche, loin du croissant.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une feuille sèche sur le banc, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une feuille sèche, collée au croissant.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8558,7 +8558,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Une feuille sèche, loin du croissant.</t>
+narrateur|Une feuille sèche, collée au croissant.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -8590,17 +8590,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le métal a failli tout glisser. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le métal glissait trop, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le métal a failli tout glisser. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le métal glissait trop, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le métal a failli tout glisser. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le métal glissait trop, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8757,7 +8757,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une feuille du toboggan reste au tissu.
-narrateur|Le métal a failli tout glisser.
+narrateur|Le métal glissait trop, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -8790,17 +8790,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Le métal du toboggan se tait, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le métal se tait, loin du col.</t>
+          <t>Le métal du toboggan se tait, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin du col, le métal se tait.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le métal du toboggan se tait, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le métal se tait, loin du col.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le métal du toboggan se tait, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin du col, le métal se tait.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le métal du toboggan se tait, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le métal se tait, loin du col.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le métal du toboggan se tait, loin. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin du col, le métal se tait.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8949,7 +8949,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le métal se tait, loin du col.</t>
+narrateur|Loin du col, le métal se tait.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -8981,17 +8981,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le bord a failli tout plier. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le bord pliait le tissu, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le bord a failli tout plier. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le bord pliait le tissu, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le bord a failli tout plier. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille du toboggan reste au tissu. Le bord pliait le tissu, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -9148,7 +9148,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une feuille du toboggan reste au tissu.
-narrateur|Le bord a failli tout plier.
+narrateur|Le bord pliait le tissu, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -9181,17 +9181,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Un pas sur la rampe, puis plus. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un pas s'éteint, sur le bois.</t>
+          <t>Un pas sur la rampe, puis plus. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur le bois, un pas s'éteint.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un pas sur la rampe, puis plus. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un pas s'éteint, sur le bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un pas sur la rampe, puis plus. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur le bois, un pas s'éteint.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un pas sur la rampe, puis plus. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un pas s'éteint, sur le bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un pas sur la rampe, puis plus. Chouchou a joué au toboggan. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur le bois, un pas s'éteint.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9340,7 +9340,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Un pas s'éteint, sur le bois.</t>
+narrateur|Sur le bois, un pas s'éteint.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -9763,17 +9763,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. L'eau a failli tout mentir. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. L'eau mentait, une seconde de trop. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. L'eau a failli tout mentir. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. L'eau mentait, une seconde de trop. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. L'eau a failli tout mentir. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. L'eau mentait, une seconde de trop. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9930,7 +9930,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une goutte du seau sèche au croissant.
-narrateur|L'eau a failli tout mentir.
+narrateur|L'eau mentait, une seconde de trop.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -9963,17 +9963,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Le seau penche, sous la rampe. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau penche, vide, sous la rampe.</t>
+          <t>Le seau penche, sous la rampe. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sous la rampe, le seau penche, vide.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau penche, sous la rampe. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau penche, vide, sous la rampe.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau penche, sous la rampe. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sous la rampe, le seau penche, vide.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau penche, sous la rampe. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau penche, vide, sous la rampe.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau penche, sous la rampe. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sous la rampe, le seau penche, vide.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le seau penche, vide, sous la rampe.</t>
+narrateur|Sous la rampe, le seau penche, vide.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -10154,17 +10154,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Le seau a failli tout verser. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Le seau versait trop, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Le seau a failli tout verser. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Le seau versait trop, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Le seau a failli tout verser. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Le seau versait trop, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10321,7 +10321,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une goutte du seau sèche au croissant.
-narrateur|Le seau a failli tout verser.
+narrateur|Le seau versait trop, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -10354,17 +10354,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le criiic du portail s'arrête. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le criiic du portail s'endort.</t>
+          <t>Le criiic du portail s'arrête. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le criiic du portail s'endort, loin.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le criiic du portail s'arrête. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le criiic du portail s'endort.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le criiic du portail s'arrête. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le criiic du portail s'endort, loin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le criiic du portail s'arrête. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le criiic du portail s'endort.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le criiic du portail s'arrête. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le criiic du portail s'endort, loin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10513,7 +10513,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le criiic du portail s'endort.</t>
+narrateur|Le criiic du portail s'endort, loin.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -10545,17 +10545,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. La goutte a failli tout cacher. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Une goutte cachait le croissant, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. La goutte a failli tout cacher. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Une goutte cachait le croissant, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. La goutte a failli tout cacher. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une goutte du seau sèche au croissant. Une goutte cachait le croissant, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10712,7 +10712,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une goutte du seau sèche au croissant.
-narrateur|La goutte a failli tout cacher.
+narrateur|Une goutte cachait le croissant, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -10745,17 +10745,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>La rampe du toboggan reste loin. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. La rampe du toboggan reste muette.</t>
+          <t>La rampe du toboggan reste loin. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin d'ici, la rampe reste muette.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La rampe du toboggan reste loin. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. La rampe du toboggan reste muette.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La rampe du toboggan reste loin. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin d'ici, la rampe reste muette.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La rampe du toboggan reste loin. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. La rampe du toboggan reste muette.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La rampe du toboggan reste loin. Chouchou a joué au toboggan. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin d'ici, la rampe reste muette.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10904,7 +10904,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|La rampe du toboggan reste muette.</t>
+narrateur|Loin d'ici, la rampe reste muette.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -11327,17 +11327,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. L'oreille a failli tout prendre. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. L'oreille prenait la place, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. L'oreille a failli tout prendre. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. L'oreille prenait la place, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. L'oreille a failli tout prendre. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. L'oreille prenait la place, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11494,7 +11494,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une feuille reste sur le doudou.
-narrateur|L'oreille a failli tout prendre.
+narrateur|L'oreille prenait la place, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -11527,17 +11527,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'oreille molle dépasse du banc. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'oreille molle dépasse, près du banc.</t>
+          <t>L'oreille molle dépasse du banc. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près du banc, une oreille molle veille.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille molle dépasse du banc. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'oreille molle dépasse, près du banc.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille molle dépasse du banc. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près du banc, une oreille molle veille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille molle dépasse du banc. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. L'oreille molle dépasse, près du banc.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille molle dépasse du banc. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près du banc, une oreille molle veille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11686,7 +11686,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|L'oreille molle dépasse, près du banc.</t>
+narrateur|Près du banc, une oreille molle veille.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -11718,17 +11718,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. Le doudou a failli tout tromper. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. Le doudou trompait l'œil, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. Le doudou a failli tout tromper. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. Le doudou trompait l'œil, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. Le doudou a failli tout tromper. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. Le doudou trompait l'œil, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une feuille reste sur le doudou.
-narrateur|Le doudou a failli tout tromper.
+narrateur|Le doudou trompait l'œil, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -11918,17 +11918,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a vu le métal, depuis le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou a le métal dans l'oreille.</t>
+          <t>Le doudou a vu le métal, depuis le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans l'oreille, un peu de métal froid.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a vu le métal, depuis le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou a le métal dans l'oreille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a vu le métal, depuis le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans l'oreille, un peu de métal froid.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a vu le métal, depuis le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou a le métal dans l'oreille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a vu le métal, depuis le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans l'oreille, un peu de métal froid.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -12077,7 +12077,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le doudou a le métal dans l'oreille.</t>
+narrateur|Dans l'oreille, un peu de métal froid.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -12109,17 +12109,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. La feuille a failli tout coller. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. La feuille collait trop, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. La feuille a failli tout coller. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. La feuille collait trop, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. La feuille a failli tout coller. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte le toboggan, croissant en main. On va au crochet, maintenant. Une feuille reste sur le doudou. La feuille collait trop, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -12276,7 +12276,7 @@
 narrateur|On quitte le toboggan, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Une feuille reste sur le doudou.
-narrateur|La feuille a failli tout coller.
+narrateur|La feuille collait trop, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -12309,17 +12309,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Un rayon a bougé, sur le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un rayon a quitté le bois.</t>
+          <t>Un rayon a bougé, sur le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur le bois, le rayon a bougé.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un rayon a bougé, sur le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un rayon a quitté le bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un rayon a bougé, sur le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur le bois, le rayon a bougé.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un rayon a bougé, sur le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Un rayon a quitté le bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un rayon a bougé, sur le bois. Chouchou a joué au toboggan. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur le bois, le rayon a bougé.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12468,7 +12468,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Un rayon a quitté le bois.</t>
+narrateur|Sur le bois, le rayon a bougé.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -13650,17 +13650,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. La corde a failli tout tenir. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. La corde tenait la manche, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. La corde a failli tout tenir. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. La corde tenait la manche, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. La corde a failli tout tenir. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle cale le ballon sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. La corde tenait la manche, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13817,7 +13817,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Un brin de corde reste au croissant.
-narrateur|La corde a failli tout tenir.
+narrateur|La corde tenait la manche, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -13850,17 +13850,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Le ballon s'endort près de l'escalier. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le ballon s'endort, près du cric.</t>
+          <t>Le ballon s'endort près de l'escalier. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près du cric, le ballon s'endort.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le ballon s'endort près de l'escalier. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le ballon s'endort, près du cric.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le ballon s'endort près de l'escalier. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près du cric, le ballon s'endort.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le ballon s'endort près de l'escalier. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le ballon s'endort, près du cric.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le ballon s'endort près de l'escalier. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près du cric, le ballon s'endort.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -14009,7 +14009,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le ballon s'endort, près du cric.</t>
+narrateur|Près du cric, le ballon s'endort.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -14041,17 +14041,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. Le cling a failli tout couvrir. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. Un cling couvrait le croissant, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. Le cling a failli tout couvrir. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. Un cling couvrait le croissant, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. Le cling a failli tout couvrir. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle cale le ballon contre le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. Un cling couvrait le croissant, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -14208,7 +14208,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Un brin de corde reste au croissant.
-narrateur|Le cling a failli tout couvrir.
+narrateur|Un cling couvrait le croissant, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -14241,17 +14241,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>La corde ne fait plus cling. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. La corde se tait, loin du col.</t>
+          <t>La corde ne fait plus cling. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin du col, la corde se tait.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La corde ne fait plus cling. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. La corde se tait, loin du col.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La corde ne fait plus cling. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin du col, la corde se tait.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La corde ne fait plus cling. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. La corde se tait, loin du col.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La corde ne fait plus cling. Chouchou a joué aux cordes. Elle a choisi le ballon, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Loin du col, la corde se tait.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -14400,7 +14400,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|La corde se tait, loin du col.</t>
+narrateur|Loin du col, la corde se tait.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -14432,17 +14432,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. L'herbe a failli tout cacher. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. L'herbe cachait le col, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. L'herbe a failli tout cacher. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. L'herbe cachait le col, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. L'herbe a failli tout cacher. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle cale le ballon sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le ballon vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Un brin de corde reste au croissant. L'herbe cachait le col, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14599,7 +14599,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Un brin de corde reste au croissant.
-narrateur|L'herbe a failli tout cacher.
+narrateur|L'herbe cachait le col, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -15214,17 +15214,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le seau a failli tout peser. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le seau pesait trop, une seconde. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le seau a failli tout peser. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le seau pesait trop, une seconde. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le seau a failli tout peser. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse l'anse sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le seau pesait trop, une seconde. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -15381,7 +15381,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'anse a senti la corde, froide.
-narrateur|Le seau a failli tout peser.
+narrateur|Le seau pesait trop, une seconde.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -15414,17 +15414,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Le seau pose son ombre sur la marche. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau pose son ombre, sur la marche.</t>
+          <t>Le seau pose son ombre sur la marche. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur la marche, l'ombre du seau dort.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau pose son ombre sur la marche. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau pose son ombre, sur la marche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau pose son ombre sur la marche. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur la marche, l'ombre du seau dort.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau pose son ombre sur la marche. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le seau pose son ombre, sur la marche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau pose son ombre sur la marche. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Sur la marche, l'ombre du seau dort.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15573,7 +15573,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le seau pose son ombre, sur la marche.</t>
+narrateur|Sur la marche, l'ombre du seau dort.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -15605,17 +15605,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. La corde a failli tout mentir. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. La corde mentait, une seconde de trop. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. La corde a failli tout mentir. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. La corde mentait, une seconde de trop. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. La corde a failli tout mentir. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse l'anse sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. La corde mentait, une seconde de trop. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15772,7 +15772,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'anse a senti la corde, froide.
-narrateur|La corde a failli tout mentir.
+narrateur|La corde mentait, une seconde de trop.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -15805,17 +15805,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Le pain tiède attend, sur la table. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le pain tiède attend, près des fraises.</t>
+          <t>Le pain tiède attend, sur la table. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près des fraises, le pain attend.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le pain tiède attend, sur la table. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le pain tiède attend, près des fraises.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le pain tiède attend, sur la table. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près des fraises, le pain attend.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le pain tiède attend, sur la table. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le pain tiède attend, près des fraises.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le pain tiède attend, sur la table. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Près des fraises, le pain attend.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15964,7 +15964,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le pain tiède attend, près des fraises.</t>
+narrateur|Près des fraises, le pain attend.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -15996,17 +15996,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le pied nu a failli tout perdre. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le pied nu manquait le bord, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le pied nu a failli tout perdre. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le pied nu manquait le bord, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le pied nu a failli tout perdre. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse l'anse sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le seau vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. L'anse a senti la corde, froide. Le pied nu manquait le bord, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -16163,7 +16163,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|L'anse a senti la corde, froide.
-narrateur|Le pied nu a failli tout perdre.
+narrateur|Le pied nu manquait le bord, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -16196,17 +16196,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Les clés de papa restent dans la coupelle. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Les clés restent dans la coupelle.</t>
+          <t>Les clés de papa restent dans la coupelle. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans la coupelle, les clés se taisent.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les clés de papa restent dans la coupelle. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Les clés restent dans la coupelle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Les clés de papa restent dans la coupelle. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans la coupelle, les clés se taisent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les clés de papa restent dans la coupelle. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Les clés restent dans la coupelle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Les clés de papa restent dans la coupelle. Chouchou a joué aux cordes. Elle a choisi le seau, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans la coupelle, les clés se taisent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -16355,7 +16355,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Les clés restent dans la coupelle.</t>
+narrateur|Dans la coupelle, les clés se taisent.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
@@ -16778,17 +16778,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le siège a failli tout confondre. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le croissant de cuivre brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le siège mélangeait les dos, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le siège a failli tout confondre. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le siège mélangeait les dos, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le siège a failli tout confondre. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le banc. Le bois des lattes est chaud, un peu. Il est dessous, je le vois ! Elle tire la manche, trop vite. Le tissu se coince entre deux lattes. Il tient, entre les lattes ! Le sourire de Chouchou disparaît. Envie et peur se bousculent, dans sa poitrine. Papa s'accroupit, à sa hauteur. Tu regardes, ou tu tires ? Je ne fonce pas. Elle écoute le bois, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, minuscule. La manche avance, puis s'arrête. Elle glisse le doudou sous la latte. Je soulève la latte, sans tirer. La manche se libère, lente, pleine. Tu l'as, sans forcer. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le siège mélangeait les dos, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16945,7 +16945,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Le doudou a l'odeur de l'herbe.
-narrateur|Le siège a failli tout confondre.
+narrateur|Le siège mélangeait les dos, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -16978,17 +16978,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a l'odeur de l'herbe. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou garde l'herbe, au chaud.</t>
+          <t>Le doudou a l'odeur de l'herbe. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au chaud, le doudou sent l'herbe.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a l'odeur de l'herbe. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou garde l'herbe, au chaud.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a l'odeur de l'herbe. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au chaud, le doudou sent l'herbe.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a l'odeur de l'herbe. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le doudou garde l'herbe, au chaud.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a l'odeur de l'herbe. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le banc. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Où s'était-il caché, sous le banc ? Sous les lattes, avec le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au chaud, le doudou sent l'herbe.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -17137,7 +17137,7 @@
 enfant-f|Sous les lattes, avec le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le doudou garde l'herbe, au chaud.</t>
+narrateur|Au chaud, le doudou sent l'herbe.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -17169,17 +17169,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le dos flou a failli tout prendre. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le croissant de cuivre clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Un dos flou prenait la place, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le dos flou a failli tout prendre. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Un dos flou prenait la place, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Le dos flou a failli tout prendre. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le portail. Le loquet est froid, un peu rêche. Il est accroché, je le vois ! Elle tire la manche, trop vite. Le tissu s'enroule autour du loquet. Le loquet le mange ! Ses épaules baissent, près du fer. Dans sa poitrine, ça serre, trop fort. Maman s'accroupit, à sa hauteur. Tu forces, ou tu regardes ? J'attends, je regarde. Elle écoute le fer, puis le col. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; clignote, minuscule. Le col glisse, puis se bloque. Elle glisse le doudou sous le loquet. Je soulève le loquet, sans tirer. La manche se libère, lente, froide. Il est à toi, maintenant. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. Un dos flou prenait la place, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -17336,7 +17336,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Le doudou a l'odeur de l'herbe.
-narrateur|Le dos flou a failli tout prendre.
+narrateur|Un dos flou prenait la place, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -17369,17 +17369,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Une fraise rentre dans le panier. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise rentre, rouge, dans le panier.</t>
+          <t>Une fraise rentre dans le panier. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans le panier, une fraise rentre.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une fraise rentre dans le panier. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise rentre, rouge, dans le panier.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une fraise rentre dans le panier. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans le panier, une fraise rentre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une fraise rentre dans le panier. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Une fraise rentre, rouge, dans le panier.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une fraise rentre dans le panier. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le portail. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait pris, au loquet ? Le loquet, et le croissant. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Dans le panier, une fraise rentre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -17528,7 +17528,7 @@
 enfant-f|Le loquet, et le croissant.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Une fraise rentre, rouge, dans le panier.</t>
+narrateur|Dans le panier, une fraise rentre.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -17560,17 +17560,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. L'odeur a failli tout perdre. Voilà le manteau, au coin des crochets.</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le croissant de cuivre brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. L'odeur égarait la main, presque. Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. L'odeur a failli tout perdre. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis level="moderate"&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. L'odeur égarait la main, presque. Voilà le manteau, au coin des crochets.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. L'odeur a failli tout perdre. Voilà le manteau, au coin des crochets. [pause]</t>
+          <t>Le croissant court vers le paillasson. La paille est rêche, couleur d'herbe. Il est plié, je le vois ! Elle tire le pli, trop vite. Le tissu se coince sous le seuil. Le seuil le garde ! Chouchou fixe le pli, sans bouger. L'envie de tirer lui pique les doigts. Papa s'accroupit, près du paillasson. Tu vois le croissant, où ? Je cherche, sans tirer. Elle écarte la paille, lente. Le &lt;emphasis&gt;croissant de cuivre&lt;/emphasis&gt; brille, sous le bord. Un pli cède, puis refuse. Elle glisse le doudou sous le bord. Je soulève le bord, sans tirer. La manche se libère, lente, rêche. Tu l'as repris, Chouchou. Chouchou serre le manteau, fière. Le doudou vient aussi, près d'elle. On quitte les cordes, croissant en main. On va au crochet, maintenant. Le doudou a l'odeur de l'herbe. L'odeur égarait la main, presque. Voilà le manteau, au coin des crochets. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17727,7 +17727,7 @@
 narrateur|On quitte les cordes, croissant en main.
 enfant-f|On va au crochet, maintenant.
 narrateur|Le doudou a l'odeur de l'herbe.
-narrateur|L'odeur a failli tout perdre.
+narrateur|L'odeur égarait la main, presque.
 narrateur|Voilà le manteau, au coin des crochets.</t>
         </is>
       </c>
@@ -17760,17 +17760,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Le couloir retrouve son cric, unique. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le croissant de cuivre se tait, au crochet.</t>
+          <t>Le couloir retrouve son cric, unique. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le croissant l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au crochet, le croissant de cuivre se tait.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le couloir retrouve son cric, unique. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le croissant de cuivre se tait, au crochet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le couloir retrouve son cric, unique. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis level="moderate"&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au crochet, le croissant de cuivre se tait.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le couloir retrouve son cric, unique. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Le croissant de cuivre se tait, au crochet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le couloir retrouve son cric, unique. Chouchou a joué aux cordes. Elle a choisi le doudou, pour le jeu. Le &lt;emphasis&gt;croissant&lt;/emphasis&gt; l'a menée vers le paillasson. Voilà le manteau rouge, sur la rampe. Au col, le croissant de cuivre brille. Il est rentré, avec sa trace. Qui l'avait plié, sur la paille ? Le paillasson, tout plat. Les fraises nous attendent, maintenant. Je croque, elle est sucrée. Au crochet, le croissant de cuivre se tait.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17919,7 +17919,7 @@
 enfant-f|Le paillasson, tout plat.
 maman|Les fraises nous attendent, maintenant.
 enfant-f|Je croque, elle est sucrée.
-narrateur|Le croissant de cuivre se tait, au crochet.</t>
+narrateur|Au crochet, le croissant de cuivre se tait.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -17945,7 +17945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -18058,6 +18058,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
